--- a/reports/member_funnel/downloads/member_funnel_1d_target_high_intent.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_target_high_intent.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F109"/>
+  <dimension ref="A1:F116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,22 +519,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>wooyes</t>
+          <t>kk_4755812472</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>01093487391</t>
+          <t>01022651918</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -575,78 +575,78 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>kk_4755812472</t>
+          <t>kk_3649011176</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>01022651918</t>
+          <t>01029317964</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kk_3649011176</t>
+          <t>antonio34</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>01029317964</t>
+          <t>01090296238</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>antonio34</t>
+          <t>kk_4814460268</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>01090296238</t>
+          <t>01064733325</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -687,22 +687,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kk_4814460268</t>
+          <t>kk_3587558636</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01064733325</t>
+          <t>01054029614</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -715,28 +715,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kk_3016906903</t>
+          <t>wjdgus5106</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01050555122</t>
+          <t>01092085106</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -771,22 +771,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kk_3587558636</t>
+          <t>kk_3016906903</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>01054029614</t>
+          <t>01050555122</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -799,22 +799,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>wjdgus5106</t>
+          <t>kk_4483270795</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01092085106</t>
+          <t>01051728139</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -827,12 +827,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>greom73</t>
+          <t>somsea</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01086372526</t>
+          <t>01028811570</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_0209_LIGHTBAG</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -855,12 +855,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>somsea</t>
+          <t>mezzo304</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>01028811570</t>
+          <t>01032400300</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EDM_0209_LIGHTBAG</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -883,22 +883,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>goril04624</t>
+          <t>kk_3817523531</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>01047651746</t>
+          <t>01090061449</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -911,12 +911,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kk_4829516327</t>
+          <t>kk_4293591148</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01098876431</t>
+          <t>01086489252</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -939,22 +939,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mezzo304</t>
+          <t>kk_3754413887</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01032400300</t>
+          <t>01063758898</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -967,22 +967,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kk_3817523531</t>
+          <t>kk_3226525569</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01090061449</t>
+          <t>01066771348</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -995,22 +995,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kk_3226525569</t>
+          <t>ilrove</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01066771348</t>
+          <t>01095892077</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>EDM_0314</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1023,22 +1023,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>kk_4293591148</t>
+          <t>kingca00769</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01086489252</t>
+          <t>01093510084</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1051,22 +1051,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kk_3754413887</t>
+          <t>kk_2921230742</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01063758898</t>
+          <t>01047459117</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1079,12 +1079,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>zollee77</t>
+          <t>kk_4279317974</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01064740702</t>
+          <t>01086395686</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1107,12 +1107,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kk_4837475331</t>
+          <t>oh8811</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01046487707</t>
+          <t>01094437389</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1122,25 +1122,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kk_4833864791</t>
+          <t>kk_4829109495</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01076696985</t>
+          <t>01096791280</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1150,25 +1150,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>oh8811</t>
+          <t>kk_4837475331</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01094437389</t>
+          <t>01046487707</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1178,25 +1178,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kk_4279317974</t>
+          <t>kk_4334202320</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01086395686</t>
+          <t>01087183625</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1206,35 +1206,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kingca00769</t>
+          <t>kk_4833864791</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01093510084</t>
+          <t>01076696985</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1247,50 +1247,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_4829109495</t>
+          <t>julee4487</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01096791280</t>
+          <t>01035614487</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kk_2921230742</t>
+          <t>phs76825</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01047459117</t>
+          <t>01091406949</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1303,12 +1303,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kk_4334202320</t>
+          <t>kk_4792317163</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01087183625</t>
+          <t>01055819917</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1331,12 +1331,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ilrove</t>
+          <t>kk_2863319761</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01095892077</t>
+          <t>01027753767</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1346,35 +1346,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>EDM_0314</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>kk_4822475920</t>
+          <t>kk_4312822884</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01073932582</t>
+          <t>01021980502</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1387,78 +1387,78 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ehdtjd3321</t>
+          <t>kk_3881036278</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01083285317</t>
+          <t>01071425586</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kk_2863319761</t>
+          <t>ehdtjd3321</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01027753767</t>
+          <t>01083285317</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>kk_4827961097</t>
+          <t>kk_2945164322</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01046347894</t>
+          <t>01031165607</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1471,12 +1471,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>hhkim1018</t>
+          <t>kk_4497254131</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01054122583</t>
+          <t>01049355494</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1486,53 +1486,53 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>EDM_0329</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kk_3672780564</t>
+          <t>sammoon26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01089459294</t>
+          <t>01055552500</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kk_3881036278</t>
+          <t>gupabaljjang</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01071425586</t>
+          <t>01027797881</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1555,40 +1555,40 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kk_4839289649</t>
+          <t>hhkim1018</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01041713878</t>
+          <t>01054122583</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>EDM_0329</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kk_4834119648</t>
+          <t>kk_3922513902</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01032402442</t>
+          <t>01063131027</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1611,22 +1611,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kk_4312822884</t>
+          <t>kk_4827961097</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01021980502</t>
+          <t>01046347894</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1639,12 +1639,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kk_4497254131</t>
+          <t>kk_4834119648</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01049355494</t>
+          <t>01032402442</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -1667,40 +1667,40 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kk_4792317163</t>
+          <t>salwoo</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01055819917</t>
+          <t>01035285763</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>julee4487</t>
+          <t>jamisu</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01035614487</t>
+          <t>01047544340</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1723,12 +1723,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>s09635</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01090472784</t>
+          <t>01046650519</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -1751,40 +1751,40 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>phs76825</t>
+          <t>kk_2954792291</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01091406949</t>
+          <t>01086049859</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>sammoon26</t>
+          <t>kk_4234864746</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01055552500</t>
+          <t>01062301880</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1794,25 +1794,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>salwoo</t>
+          <t>kk_4422614826</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01035285763</t>
+          <t>01067869772</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -1835,12 +1835,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kk_3922513902</t>
+          <t>chcjddl</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01063131027</t>
+          <t>01086228198</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1850,53 +1850,53 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0226_EFW</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>gupabaljjang</t>
+          <t>iamgabi0</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01027797881</t>
+          <t>01028422324</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_2945164322</t>
+          <t>kk_4318643192</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01031165607</t>
+          <t>01062525049</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1906,25 +1906,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>jamisu</t>
+          <t>kjchan69</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01047544340</t>
+          <t>01063792010</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -1947,12 +1947,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>chcjddl</t>
+          <t>kk_3605280738</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01086228198</t>
+          <t>01063779875</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_EFW</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -1975,40 +1975,40 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kjchan69</t>
+          <t>kk_4840537683</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01063792010</t>
+          <t>01085206466</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kk_4422614826</t>
+          <t>kk_2824348249</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01067869772</t>
+          <t>01025435357</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2031,22 +2031,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kk_2824348249</t>
+          <t>luxurykim11</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01025435357</t>
+          <t>01093252716</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -2059,12 +2059,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>luxurykim11</t>
+          <t>kk_3101303470</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01093252716</t>
+          <t>01065980201</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -2087,12 +2087,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>hhgg6482</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01046650519</t>
+          <t>01052195642</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2102,63 +2102,63 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_3605280738</t>
+          <t>kk_2805794827</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01063779875</t>
+          <t>01098906270</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_4326567662</t>
+          <t>kk_4839277282</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01046049921</t>
+          <t>01045519906</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -2171,22 +2171,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kk_4836613952</t>
+          <t>ymvianne</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01041344927</t>
+          <t>01091979009</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -2199,50 +2199,50 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_4318643192</t>
+          <t>kk_4838986411</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01062525049</t>
+          <t>01093175607</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kk_2954792291</t>
+          <t>kk_4837599586</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01086049859</t>
+          <t>01026751676</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2255,12 +2255,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kk_4234864746</t>
+          <t>kk_4679052952</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01062301880</t>
+          <t>01053553195</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2270,35 +2270,35 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>iamgabi0</t>
+          <t>queen704</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01028422324</t>
+          <t>01030909790</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -2311,50 +2311,50 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_4836691459</t>
+          <t>kk_4840738116</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01072445075</t>
+          <t>01041260767</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ymvianne</t>
+          <t>kk_4817163496</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01091979009</t>
+          <t>01035959174</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -2367,134 +2367,134 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_3101303470</t>
+          <t>kk_4535433913</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01065980201</t>
+          <t>01071714088</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MESSAGE_0325_TRAIL</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kk_4741668082</t>
+          <t>kk_4837856932</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01035796093</t>
+          <t>01042710870</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kk_4839277282</t>
+          <t>miraekoss</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01045519906</t>
+          <t>01020213203</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kk_4281300201</t>
+          <t>kk_4741668082</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01044488385</t>
+          <t>01035796093</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kk_4838507875</t>
+          <t>kk_3688266936</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01041366853</t>
+          <t>01031949749</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -2507,22 +2507,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_4838986411</t>
+          <t>kk_4841152170</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01093175607</t>
+          <t>01050200309</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -2535,12 +2535,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_4533637391</t>
+          <t>kk_4281300201</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01090803497</t>
+          <t>01044488385</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2563,17 +2563,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kk_4679052952</t>
+          <t>kk_3205887201</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01053553195</t>
+          <t>01063328335</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2591,106 +2591,106 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_4817163496</t>
+          <t>kk_4841179120</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01035959174</t>
+          <t>01068577665</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_3205887201</t>
+          <t>kk_4840949436</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01063328335</t>
+          <t>01064495993</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_4837856932</t>
+          <t>kk_4840338408</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01042710870</t>
+          <t>01054621177</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_4840292707</t>
+          <t>kk_4815312274</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01085257253</t>
+          <t>01050357610</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -2703,78 +2703,78 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>hhgg6482</t>
+          <t>kk_4841155697</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01052195642</t>
+          <t>01041762160</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kk_4815312274</t>
+          <t>kk_4838507875</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01050357610</t>
+          <t>01041366853</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_4485686054</t>
+          <t>kk_4841564061</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01030613096</t>
+          <t>01088968580</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -2787,78 +2787,78 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_2805794827</t>
+          <t>kk_4533637391</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01098906270</t>
+          <t>01090803497</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>hw00185</t>
+          <t>kk_3803785598</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01032596566</t>
+          <t>01084494003</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kk_4840338408</t>
+          <t>kk_3483369286</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01054621177</t>
+          <t>01088087188</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -2871,22 +2871,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>queen704</t>
+          <t>cloud84</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01030909790</t>
+          <t>01094808884</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EDM_0411</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -2899,50 +2899,50 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_4535433913</t>
+          <t>kk_4303227124</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01071714088</t>
+          <t>01037747441</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_TRAIL</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kk_3803785598</t>
+          <t>alswjd7015</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01084494003</t>
+          <t>01039137015</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -2983,22 +2983,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kk_4200407916</t>
+          <t>kk_3671070277</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01032980786</t>
+          <t>01065561446</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -3011,106 +3011,106 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kk_4303227124</t>
+          <t>kk_4305076317</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01037747441</t>
+          <t>01082835869</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_3181933743</t>
+          <t>kk_3721509519</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01024077112</t>
+          <t>01097118472</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_PRODUCT2</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_4439122782</t>
+          <t>kk_4200407916</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01028252500</t>
+          <t>01032980786</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>cloud84</t>
+          <t>kk_4840930255</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01094808884</t>
+          <t>01092600071</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3123,22 +3123,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>kk_3688266936</t>
+          <t>kk_4841095079</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01031949749</t>
+          <t>01050906999</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -3151,22 +3151,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>jyyon101</t>
+          <t>kk_4840763633</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01050119990</t>
+          <t>01048116274</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -3179,50 +3179,50 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>dpfmxkdl</t>
+          <t>kk_4841470777</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01023221625</t>
+          <t>01067860344</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>hisgogo</t>
+          <t>halla1001</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01054110956</t>
+          <t>01097612449</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
@@ -3235,50 +3235,50 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_3483369286</t>
+          <t>kk_3181933743</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01088087188</t>
+          <t>01024077112</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>halla1001</t>
+          <t>eumban</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01097612449</t>
+          <t>01089805431</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -3291,106 +3291,106 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_3721509519</t>
+          <t>acp1011</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01097118472</t>
+          <t>01045809723</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>eumban</t>
+          <t>akilris</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01089805431</t>
+          <t>01076225525</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_3671070277</t>
+          <t>kk_4568748102</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01065561446</t>
+          <t>01054073523</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>alswjd7015</t>
+          <t>kk_4840658838</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01039137015</t>
+          <t>01039292600</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
@@ -3403,22 +3403,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>akilris</t>
+          <t>kk_4841572668</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01076225525</t>
+          <t>01024164342</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
@@ -3431,22 +3431,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>mwnew5</t>
+          <t>jyyon101</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01091343604</t>
+          <t>01050119990</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -3459,12 +3459,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_4305076317</t>
+          <t>dpfmxkdl</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01082835869</t>
+          <t>01023221625</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3474,13 +3474,209 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>manong0821</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>01036923281</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LMS_ECOM_0410exclusive2</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>kk_4840669442</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>01093940957</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>jyseoul</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>01054813799</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>kk_4840846776</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>01055961435</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>[PF]전환_회원가입(유사)</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>mwnew5</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>01091343604</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>hisgogo</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>01054110956</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>kk_4840872605</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>01063782216</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>(organic)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1d_target_high_intent.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_target_high_intent.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F116"/>
+  <dimension ref="A1:F115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,22 +519,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kk_4755812472</t>
+          <t>kk_4270962450</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>01022651918</t>
+          <t>01065174170</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -547,22 +547,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>kk_4270962450</t>
+          <t>kk_4755812472</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>01065174170</t>
+          <t>01022651918</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -687,12 +687,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kk_3587558636</t>
+          <t>josolha</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01054029614</t>
+          <t>01052056266</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -715,50 +715,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>wjdgus5106</t>
+          <t>kk_3587558636</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01092085106</t>
+          <t>01054029614</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>josolha</t>
+          <t>kk_3016906903</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>01052056266</t>
+          <t>01050555122</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -771,50 +771,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kk_3016906903</t>
+          <t>kk_4483270795</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>01050555122</t>
+          <t>01051728139</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kk_4483270795</t>
+          <t>wjdgus5106</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01051728139</t>
+          <t>01092085106</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -911,12 +911,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kk_4293591148</t>
+          <t>kk_3754413887</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01086489252</t>
+          <t>01063758898</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -939,22 +939,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kk_3754413887</t>
+          <t>ilrove</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01063758898</t>
+          <t>01095892077</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>EDM_0314</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -967,22 +967,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kk_3226525569</t>
+          <t>kk_4293591148</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01066771348</t>
+          <t>01086489252</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -995,22 +995,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ilrove</t>
+          <t>kk_3226525569</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01095892077</t>
+          <t>01066771348</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EDM_0314</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1023,12 +1023,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>kingca00769</t>
+          <t>kk_4279317974</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01093510084</t>
+          <t>01086395686</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1051,22 +1051,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kk_2921230742</t>
+          <t>oh8811</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01047459117</t>
+          <t>01094437389</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1079,12 +1079,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kk_4279317974</t>
+          <t>kk_4334202320</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01086395686</t>
+          <t>01087183625</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1094,25 +1094,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>oh8811</t>
+          <t>kingca00769</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01094437389</t>
+          <t>01093510084</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1135,22 +1135,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kk_4829109495</t>
+          <t>kk_4837475331</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01096791280</t>
+          <t>01046487707</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1163,50 +1163,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>kk_4837475331</t>
+          <t>kk_2921230742</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01046487707</t>
+          <t>01047459117</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kk_4334202320</t>
+          <t>kk_4829109495</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01087183625</t>
+          <t>01096791280</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1247,12 +1247,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>julee4487</t>
+          <t>phs76825</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01035614487</t>
+          <t>01091406949</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1275,12 +1275,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>phs76825</t>
+          <t>gupabaljjang</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01091406949</t>
+          <t>01027797881</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1290,25 +1290,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kk_4792317163</t>
+          <t>sammoon26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01055819917</t>
+          <t>01055552500</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1359,22 +1359,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>kk_4312822884</t>
+          <t>julee4487</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01021980502</t>
+          <t>01035614487</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1387,12 +1387,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kk_3881036278</t>
+          <t>kk_4834119648</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01071425586</t>
+          <t>01032402442</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1402,63 +1402,63 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ehdtjd3321</t>
+          <t>kk_4792317163</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01083285317</t>
+          <t>01055819917</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>kk_2945164322</t>
+          <t>salwoo</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01031165607</t>
+          <t>01035285763</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1471,12 +1471,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kk_4497254131</t>
+          <t>hhkim1018</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01049355494</t>
+          <t>01054122583</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1486,25 +1486,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>EDM_0329</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>sammoon26</t>
+          <t>kk_3922513902</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01055552500</t>
+          <t>01063131027</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1514,91 +1514,91 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>gupabaljjang</t>
+          <t>kk_4312822884</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01027797881</t>
+          <t>01021980502</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>hhkim1018</t>
+          <t>ehdtjd3321</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01054122583</t>
+          <t>01083285317</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>EDM_0329</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kk_3922513902</t>
+          <t>kk_4827961097</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01063131027</t>
+          <t>01046347894</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1611,40 +1611,40 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kk_4827961097</t>
+          <t>kk_3881036278</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01046347894</t>
+          <t>01071425586</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kk_4834119648</t>
+          <t>kk_4497254131</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01032402442</t>
+          <t>01049355494</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -1667,22 +1667,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>salwoo</t>
+          <t>kk_2945164322</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01035285763</t>
+          <t>01031165607</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -1695,12 +1695,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>jamisu</t>
+          <t>kk_2824348249</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01047544340</t>
+          <t>01025435357</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -1723,22 +1723,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4422614826</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01046650519</t>
+          <t>01067869772</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -1751,28 +1751,28 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>kk_2954792291</t>
+          <t>kjchan69</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01086049859</t>
+          <t>01063792010</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -1807,40 +1807,40 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kk_4422614826</t>
+          <t>kk_4840537683</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01067869772</t>
+          <t>01085206466</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>chcjddl</t>
+          <t>kk_3605280738</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01086228198</t>
+          <t>01063779875</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_EFW</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -1863,12 +1863,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>iamgabi0</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01028422324</t>
+          <t>01046650519</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1891,12 +1891,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_4318643192</t>
+          <t>jamisu</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01062525049</t>
+          <t>01047544340</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1906,25 +1906,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kjchan69</t>
+          <t>kk_4318643192</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01063792010</t>
+          <t>01062525049</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1934,35 +1934,35 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>kk_3605280738</t>
+          <t>kk_2954792291</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01063779875</t>
+          <t>01086049859</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -1975,22 +1975,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kk_4840537683</t>
+          <t>chcjddl</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01085206466</t>
+          <t>01086228198</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>KAKAO_CH_MENU_0226_EFW</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2003,22 +2003,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kk_2824348249</t>
+          <t>iamgabi0</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01025435357</t>
+          <t>01028422324</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2059,12 +2059,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kk_3101303470</t>
+          <t>kk_3205887201</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01065980201</t>
+          <t>01063328335</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2074,35 +2074,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>hhgg6482</t>
+          <t>kk_4679052952</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01052195642</t>
+          <t>01053553195</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2115,12 +2115,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_2805794827</t>
+          <t>kk_4837856932</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01098906270</t>
+          <t>01042710870</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2130,63 +2130,63 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_4839277282</t>
+          <t>kk_4533637391</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01045519906</t>
+          <t>01090803497</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ymvianne</t>
+          <t>queen704</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01091979009</t>
+          <t>01030909790</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -2199,22 +2199,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_4838986411</t>
+          <t>kk_4839277282</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01093175607</t>
+          <t>01045519906</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2227,12 +2227,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kk_4837599586</t>
+          <t>kk_4841155697</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01026751676</t>
+          <t>01041762160</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2242,35 +2242,35 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kk_4679052952</t>
+          <t>hhgg6482</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01053553195</t>
+          <t>01052195642</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -2283,78 +2283,78 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>queen704</t>
+          <t>miraekoss</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01030909790</t>
+          <t>01020213203</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_4840738116</t>
+          <t>kk_4815312274</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01041260767</t>
+          <t>01050357610</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kk_4817163496</t>
+          <t>kk_4841152170</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01035959174</t>
+          <t>01050200309</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -2367,12 +2367,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_4535433913</t>
+          <t>kk_4841179120</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01071714088</t>
+          <t>01068577665</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_TRAIL</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -2395,22 +2395,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kk_4837856932</t>
+          <t>kk_3688266936</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01042710870</t>
+          <t>01031949749</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -2423,12 +2423,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>miraekoss</t>
+          <t>kk_2805794827</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01020213203</t>
+          <t>01098906270</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2438,25 +2438,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kk_4741668082</t>
+          <t>kk_3101303470</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01035796093</t>
+          <t>01065980201</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -2479,22 +2479,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kk_3688266936</t>
+          <t>kk_4838507875</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01031949749</t>
+          <t>01041366853</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -2507,12 +2507,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_4841152170</t>
+          <t>kk_4840338408</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01050200309</t>
+          <t>01054621177</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2535,22 +2535,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_4281300201</t>
+          <t>kk_3803785598</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01044488385</t>
+          <t>01084494003</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -2563,12 +2563,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kk_3205887201</t>
+          <t>kk_4838986411</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01063328335</t>
+          <t>01093175607</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2578,53 +2578,53 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_4841179120</t>
+          <t>kk_4741668082</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01068577665</t>
+          <t>01035796093</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_4840949436</t>
+          <t>kk_4281300201</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01064495993</t>
+          <t>01044488385</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2634,53 +2634,53 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_4840338408</t>
+          <t>kk_4837599586</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01054621177</t>
+          <t>01026751676</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_4815312274</t>
+          <t>kk_4817163496</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01050357610</t>
+          <t>01035959174</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -2703,78 +2703,78 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kk_4841155697</t>
+          <t>kk_4840738116</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01041762160</t>
+          <t>01041260767</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kk_4838507875</t>
+          <t>kk_4841564061</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01041366853</t>
+          <t>01088968580</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_4841564061</t>
+          <t>ymvianne</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01088968580</t>
+          <t>01091979009</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -2787,12 +2787,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_4533637391</t>
+          <t>kk_4840949436</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01090803497</t>
+          <t>01064495993</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2802,35 +2802,35 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_3803785598</t>
+          <t>kk_4535433913</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01084494003</t>
+          <t>01071714088</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_MESSAGE_0325_TRAIL</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -2843,50 +2843,50 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kk_3483369286</t>
+          <t>dpfmxkdl</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01088087188</t>
+          <t>01023221625</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>cloud84</t>
+          <t>akilris</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01094808884</t>
+          <t>01076225525</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>EDM_0411</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -2899,50 +2899,50 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_4303227124</t>
+          <t>kk_3671070277</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01037747441</t>
+          <t>01065561446</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>alswjd7015</t>
+          <t>mwnew5</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01039137015</t>
+          <t>01091343604</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -2955,12 +2955,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_4204337741</t>
+          <t>cloud84</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01085530637</t>
+          <t>01094808884</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2970,53 +2970,53 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_0411</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kk_3671070277</t>
+          <t>kk_4840930255</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01065561446</t>
+          <t>01092600071</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kk_4305076317</t>
+          <t>manong0821</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01082835869</t>
+          <t>01036923281</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3039,12 +3039,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_3721509519</t>
+          <t>kk_4841095079</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01097118472</t>
+          <t>01050906999</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3054,53 +3054,53 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_4200407916</t>
+          <t>kk_4841572668</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01032980786</t>
+          <t>01024164342</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>kk_4840930255</t>
+          <t>kk_3721509519</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01092600071</t>
+          <t>01097118472</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3123,12 +3123,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>kk_4841095079</t>
+          <t>kk_4841470777</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01050906999</t>
+          <t>01067860344</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3138,35 +3138,35 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_4840763633</t>
+          <t>alswjd7015</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01048116274</t>
+          <t>01039137015</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -3179,40 +3179,40 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_4841470777</t>
+          <t>eumban</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01067860344</t>
+          <t>01089805431</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>halla1001</t>
+          <t>acp1011</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01097612449</t>
+          <t>01045809723</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
@@ -3235,22 +3235,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_3181933743</t>
+          <t>halla1001</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01024077112</t>
+          <t>01097612449</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -3263,22 +3263,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>eumban</t>
+          <t>kk_4840763633</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01089805431</t>
+          <t>01048116274</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -3291,22 +3291,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>acp1011</t>
+          <t>kk_4840669442</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01045809723</t>
+          <t>01093940957</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -3319,28 +3319,28 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>akilris</t>
+          <t>kk_4200407916</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01076225525</t>
+          <t>01032980786</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -3375,22 +3375,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_4840658838</t>
+          <t>kk_4305076317</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01039292600</t>
+          <t>01082835869</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
@@ -3403,68 +3403,68 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_4841572668</t>
+          <t>hisgogo</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01024164342</t>
+          <t>01054110956</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>jyyon101</t>
+          <t>kk_4840872605</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01050119990</t>
+          <t>01063782216</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>dpfmxkdl</t>
+          <t>kk_3181933743</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01023221625</t>
+          <t>01024077112</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
@@ -3487,22 +3487,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>manong0821</t>
+          <t>kk_4840658838</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01036923281</t>
+          <t>01039292600</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -3515,22 +3515,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kk_4840669442</t>
+          <t>kk_4840846776</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01093940957</t>
+          <t>01055961435</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -3543,12 +3543,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>jyseoul</t>
+          <t>kk_4303227124</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01054813799</t>
+          <t>01037747441</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -3571,22 +3571,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kk_4840846776</t>
+          <t>kk_4204337741</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01055961435</t>
+          <t>01085530637</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -3599,22 +3599,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>mwnew5</t>
+          <t>jyyon101</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01091343604</t>
+          <t>01050119990</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -3627,12 +3627,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>hisgogo</t>
+          <t>kk_3483369286</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01054110956</t>
+          <t>01088087188</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3647,34 +3647,6 @@
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
-        <is>
-          <t>HIGH_INTENT_NUDGE</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>kk_4840872605</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>01063782216</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Organic Traffic</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>(organic)</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
         </is>
